--- a/vtiger-crm-a4-pro-max/src/test/resources/tsd.xlsx
+++ b/vtiger-crm-a4-pro-max/src/test/resources/tsd.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="org" sheetId="1" r:id="rId1"/>
@@ -22,37 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>orgName</t>
-  </si>
-  <si>
-    <t>qspiders_</t>
-  </si>
-  <si>
-    <t>pyspiders_</t>
-  </si>
-  <si>
-    <t>prospiders_</t>
-  </si>
-  <si>
-    <t>jspiders_</t>
-  </si>
-  <si>
-    <t>globalspiders_</t>
-  </si>
-  <si>
-    <t>testYantra_</t>
-  </si>
-  <si>
-    <t>fireflink_</t>
-  </si>
-  <si>
-    <t>robowaves_</t>
-  </si>
-  <si>
-    <t>tekPyramid_</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="282">
   <si>
     <t>lastName</t>
   </si>
@@ -88,19 +58,834 @@
   </si>
   <si>
     <t>gandhi ji</t>
+  </si>
+  <si>
+    <t>Organization Name</t>
+  </si>
+  <si>
+    <t>Organization No</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Ticker Symbol</t>
+  </si>
+  <si>
+    <t>Fax</t>
+  </si>
+  <si>
+    <t>Member Of</t>
+  </si>
+  <si>
+    <t>Other Phone</t>
+  </si>
+  <si>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Other Email</t>
+  </si>
+  <si>
+    <t>Ownership</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>SIC Code</t>
+  </si>
+  <si>
+    <t>Email Opt Out</t>
+  </si>
+  <si>
+    <t>Annual Revenue ($)</t>
+  </si>
+  <si>
+    <t>Assigned To Type</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Notify Owner</t>
+  </si>
+  <si>
+    <t>Billing Address</t>
+  </si>
+  <si>
+    <t>Shipping Address</t>
+  </si>
+  <si>
+    <t>Billing PO Box</t>
+  </si>
+  <si>
+    <t>Shipping PO Box</t>
+  </si>
+  <si>
+    <t>Billing City</t>
+  </si>
+  <si>
+    <t>Shipping City</t>
+  </si>
+  <si>
+    <t>Billing State</t>
+  </si>
+  <si>
+    <t>Shipping State</t>
+  </si>
+  <si>
+    <t>Billing Postal Code</t>
+  </si>
+  <si>
+    <t>Shipping Postal Code</t>
+  </si>
+  <si>
+    <t>Billing Country</t>
+  </si>
+  <si>
+    <t>Shipping Country</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>QSpiders</t>
+  </si>
+  <si>
+    <t>ORG-1001</t>
+  </si>
+  <si>
+    <t>https://www.qspiders.example</t>
+  </si>
+  <si>
+    <t>+91-9801000001</t>
+  </si>
+  <si>
+    <t>TICK01</t>
+  </si>
+  <si>
+    <t>+91-79-40000001</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>+91-9701110001</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>contact1@qspiders.example</t>
+  </si>
+  <si>
+    <t>info1@qspiders.example</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>$125000</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>ACOE Fireflink</t>
+  </si>
+  <si>
+    <t>101 Demo Street, Building 1</t>
+  </si>
+  <si>
+    <t>201 Sample Avenue, Floor 1</t>
+  </si>
+  <si>
+    <t>POB-501</t>
+  </si>
+  <si>
+    <t>POB-701</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Noida</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh</t>
+  </si>
+  <si>
+    <t>380001</t>
+  </si>
+  <si>
+    <t>380101</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Demo organization record 1 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>PySpiders</t>
+  </si>
+  <si>
+    <t>ORG-1002</t>
+  </si>
+  <si>
+    <t>https://www.pyspiders.example</t>
+  </si>
+  <si>
+    <t>+91-9802000002</t>
+  </si>
+  <si>
+    <t>TICK02</t>
+  </si>
+  <si>
+    <t>+91-79-40000002</t>
+  </si>
+  <si>
+    <t>+91-9702110002</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>contact2@pyspiders.example</t>
+  </si>
+  <si>
+    <t>info2@pyspiders.example</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>$250000</t>
+  </si>
+  <si>
+    <t>102 Demo Street, Building 2</t>
+  </si>
+  <si>
+    <t>202 Sample Avenue, Floor 2</t>
+  </si>
+  <si>
+    <t>POB-502</t>
+  </si>
+  <si>
+    <t>POB-702</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>380002</t>
+  </si>
+  <si>
+    <t>380102</t>
+  </si>
+  <si>
+    <t>Demo organization record 2 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>ProSpiders</t>
+  </si>
+  <si>
+    <t>ORG-1003</t>
+  </si>
+  <si>
+    <t>https://www.prospiders.example</t>
+  </si>
+  <si>
+    <t>+91-9803000003</t>
+  </si>
+  <si>
+    <t>TICK03</t>
+  </si>
+  <si>
+    <t>+91-79-40000003</t>
+  </si>
+  <si>
+    <t>TestYantra</t>
+  </si>
+  <si>
+    <t>+91-9703110003</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>contact3@prospiders.example</t>
+  </si>
+  <si>
+    <t>info3@prospiders.example</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Prospect</t>
+  </si>
+  <si>
+    <t>0003</t>
+  </si>
+  <si>
+    <t>$375000</t>
+  </si>
+  <si>
+    <t>103 Demo Street, Building 3</t>
+  </si>
+  <si>
+    <t>203 Sample Avenue, Floor 3</t>
+  </si>
+  <si>
+    <t>POB-503</t>
+  </si>
+  <si>
+    <t>POB-703</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>380003</t>
+  </si>
+  <si>
+    <t>380103</t>
+  </si>
+  <si>
+    <t>Demo organization record 3 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>JSpiders</t>
+  </si>
+  <si>
+    <t>ORG-1004</t>
+  </si>
+  <si>
+    <t>https://www.jspiders.example</t>
+  </si>
+  <si>
+    <t>+91-9804000004</t>
+  </si>
+  <si>
+    <t>TICK04</t>
+  </si>
+  <si>
+    <t>+91-79-40000004</t>
+  </si>
+  <si>
+    <t>GlobalSpiders</t>
+  </si>
+  <si>
+    <t>+91-9704110004</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>contact4@jspiders.example</t>
+  </si>
+  <si>
+    <t>info4@jspiders.example</t>
+  </si>
+  <si>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>Consulting</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>0004</t>
+  </si>
+  <si>
+    <t>$500000</t>
+  </si>
+  <si>
+    <t>104 Demo Street, Building 4</t>
+  </si>
+  <si>
+    <t>204 Sample Avenue, Floor 4</t>
+  </si>
+  <si>
+    <t>POB-504</t>
+  </si>
+  <si>
+    <t>POB-704</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>380004</t>
+  </si>
+  <si>
+    <t>380104</t>
+  </si>
+  <si>
+    <t>Demo organization record 4 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>ORG-1005</t>
+  </si>
+  <si>
+    <t>https://www.globalspiders.example</t>
+  </si>
+  <si>
+    <t>+91-9805000005</t>
+  </si>
+  <si>
+    <t>TICK05</t>
+  </si>
+  <si>
+    <t>+91-79-40000005</t>
+  </si>
+  <si>
+    <t>+91-9705110005</t>
+  </si>
+  <si>
+    <t>625</t>
+  </si>
+  <si>
+    <t>contact5@globalspiders.example</t>
+  </si>
+  <si>
+    <t>info5@globalspiders.example</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>$625000</t>
+  </si>
+  <si>
+    <t>105 Demo Street, Building 5</t>
+  </si>
+  <si>
+    <t>205 Sample Avenue, Floor 5</t>
+  </si>
+  <si>
+    <t>POB-505</t>
+  </si>
+  <si>
+    <t>POB-705</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>380005</t>
+  </si>
+  <si>
+    <t>380105</t>
+  </si>
+  <si>
+    <t>Demo organization record 5 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>ORG-1006</t>
+  </si>
+  <si>
+    <t>https://www.testyantra.example</t>
+  </si>
+  <si>
+    <t>+91-9806000006</t>
+  </si>
+  <si>
+    <t>TICK06</t>
+  </si>
+  <si>
+    <t>+91-79-40000006</t>
+  </si>
+  <si>
+    <t>+91-9706110006</t>
+  </si>
+  <si>
+    <t>750</t>
+  </si>
+  <si>
+    <t>contact6@testyantra.example</t>
+  </si>
+  <si>
+    <t>info6@testyantra.example</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>0006</t>
+  </si>
+  <si>
+    <t>$750000</t>
+  </si>
+  <si>
+    <t>106 Demo Street, Building 6</t>
+  </si>
+  <si>
+    <t>206 Sample Avenue, Floor 6</t>
+  </si>
+  <si>
+    <t>POB-506</t>
+  </si>
+  <si>
+    <t>POB-706</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>380006</t>
+  </si>
+  <si>
+    <t>380106</t>
+  </si>
+  <si>
+    <t>Demo organization record 6 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>FireFlink</t>
+  </si>
+  <si>
+    <t>ORG-1007</t>
+  </si>
+  <si>
+    <t>https://www.fireflink.example</t>
+  </si>
+  <si>
+    <t>+91-9807000007</t>
+  </si>
+  <si>
+    <t>TICK07</t>
+  </si>
+  <si>
+    <t>+91-79-40000007</t>
+  </si>
+  <si>
+    <t>+91-9707110007</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>contact7@fireflink.example</t>
+  </si>
+  <si>
+    <t>info7@fireflink.example</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t>$875000</t>
+  </si>
+  <si>
+    <t>107 Demo Street, Building 7</t>
+  </si>
+  <si>
+    <t>207 Sample Avenue, Floor 7</t>
+  </si>
+  <si>
+    <t>POB-507</t>
+  </si>
+  <si>
+    <t>POB-707</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Tamil Nadu</t>
+  </si>
+  <si>
+    <t>380007</t>
+  </si>
+  <si>
+    <t>380107</t>
+  </si>
+  <si>
+    <t>Demo organization record 7 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>RoboWaves</t>
+  </si>
+  <si>
+    <t>ORG-1008</t>
+  </si>
+  <si>
+    <t>https://www.robowaves.example</t>
+  </si>
+  <si>
+    <t>+91-9808000008</t>
+  </si>
+  <si>
+    <t>TICK08</t>
+  </si>
+  <si>
+    <t>+91-79-40000008</t>
+  </si>
+  <si>
+    <t>+91-9708110008</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>contact8@robowaves.example</t>
+  </si>
+  <si>
+    <t>info8@robowaves.example</t>
+  </si>
+  <si>
+    <t>Software Testing</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>$1000000</t>
+  </si>
+  <si>
+    <t>108 Demo Street, Building 8</t>
+  </si>
+  <si>
+    <t>208 Sample Avenue, Floor 8</t>
+  </si>
+  <si>
+    <t>POB-508</t>
+  </si>
+  <si>
+    <t>POB-708</t>
+  </si>
+  <si>
+    <t>Surat</t>
+  </si>
+  <si>
+    <t>380008</t>
+  </si>
+  <si>
+    <t>380108</t>
+  </si>
+  <si>
+    <t>Demo organization record 8 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>TekPyramid</t>
+  </si>
+  <si>
+    <t>ORG-1009</t>
+  </si>
+  <si>
+    <t>https://www.tekpyramid.example</t>
+  </si>
+  <si>
+    <t>+91-9809000009</t>
+  </si>
+  <si>
+    <t>TICK09</t>
+  </si>
+  <si>
+    <t>+91-79-40000009</t>
+  </si>
+  <si>
+    <t>+91-9709110009</t>
+  </si>
+  <si>
+    <t>1125</t>
+  </si>
+  <si>
+    <t>contact9@tekpyramid.example</t>
+  </si>
+  <si>
+    <t>info9@tekpyramid.example</t>
+  </si>
+  <si>
+    <t>Cloud Services</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>$1125000</t>
+  </si>
+  <si>
+    <t>109 Demo Street, Building 9</t>
+  </si>
+  <si>
+    <t>209 Sample Avenue, Floor 9</t>
+  </si>
+  <si>
+    <t>POB-509</t>
+  </si>
+  <si>
+    <t>POB-709</t>
+  </si>
+  <si>
+    <t>Gandhinagar</t>
+  </si>
+  <si>
+    <t>380009</t>
+  </si>
+  <si>
+    <t>380109</t>
+  </si>
+  <si>
+    <t>Demo organization record 9 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>AutomationWithPiyush</t>
+  </si>
+  <si>
+    <t>ORG-1010</t>
+  </si>
+  <si>
+    <t>https://www.automationwithpiyush.example</t>
+  </si>
+  <si>
+    <t>+91-9810000010</t>
+  </si>
+  <si>
+    <t>TICK10</t>
+  </si>
+  <si>
+    <t>+91-79-40000010</t>
+  </si>
+  <si>
+    <t>+91-9710110010</t>
+  </si>
+  <si>
+    <t>1250</t>
+  </si>
+  <si>
+    <t>contact10@automationwithpiyush.example</t>
+  </si>
+  <si>
+    <t>info10@automationwithpiyush.example</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>$1250000</t>
+  </si>
+  <si>
+    <t>110 Demo Street, Building 10</t>
+  </si>
+  <si>
+    <t>210 Sample Avenue, Floor 10</t>
+  </si>
+  <si>
+    <t>POB-510</t>
+  </si>
+  <si>
+    <t>POB-710</t>
+  </si>
+  <si>
+    <t>380010</t>
+  </si>
+  <si>
+    <t>380110</t>
+  </si>
+  <si>
+    <t>Demo organization record 10 for CRM automation testing</t>
+  </si>
+  <si>
+    <t>TestYantra_</t>
+  </si>
+  <si>
+    <t>companyName</t>
+  </si>
+  <si>
+    <t>ceat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -144,11 +929,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,60 +1218,1185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="52.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG3" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH3" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD4" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH4" s="5" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB5" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AD5" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="AF5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH5" s="5" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC6" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD6" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AF6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH6" s="5" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="AE7" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC8" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD8" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH8" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE9" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH9" s="5" t="s">
+        <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="Z10" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD10" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="AE10" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="AF10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH10" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z11" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD11" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="AE11" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH11" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -492,68 +2406,87 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="B11" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="B12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
